--- a/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\Week 14\Week 14\ams_weekly_data\Audio_Array\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1731C976-1305-4B7B-BEED-452439283C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\ams_weekly_data\Audio_Array\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1731C976-1305-4B7B-BEED-452439283C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E612C6C1-2F9B-41D5-8EC9-0E534D64DB3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{C2EB3544-0B30-4B5A-9817-98DE85FBF6BC}"/>
   </bookViews>
   <sheets>
     <sheet name="SP" sheetId="1" r:id="rId1"/>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
@@ -12747,7 +12747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12971,23 +12971,23 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>B0B4G8PH2P</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>23966.33333333333</v>
+        <v>7866</v>
       </c>
       <c r="E7" t="n">
-        <v>85.33333333333333</v>
+        <v>28</v>
       </c>
       <c r="F7" t="n">
-        <v>692.7033333333334</v>
+        <v>227.3613934043357</v>
       </c>
       <c r="G7" t="n">
-        <v>6382.203333333334</v>
+        <v>2094.788018232618</v>
       </c>
       <c r="H7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -13004,23 +13004,23 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0D3Q2T5XX</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>23966.33333333333</v>
+        <v>52501</v>
       </c>
       <c r="E8" t="n">
-        <v>85.33333333333333</v>
+        <v>187</v>
       </c>
       <c r="F8" t="n">
-        <v>692.7033333333334</v>
+        <v>1517.452385149844</v>
       </c>
       <c r="G8" t="n">
-        <v>6382.203333333334</v>
+        <v>13981.00630478361</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -13037,23 +13037,23 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23966.33333333333</v>
+        <v>11531</v>
       </c>
       <c r="E9" t="n">
-        <v>85.33333333333333</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>692.7033333333334</v>
+        <v>333.2962214458202</v>
       </c>
       <c r="G9" t="n">
-        <v>6382.203333333334</v>
+        <v>3070.815676983776</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -13173,19 +13173,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24836</v>
+        <v>44771</v>
       </c>
       <c r="E13" t="n">
-        <v>126.6666666666667</v>
+        <v>228</v>
       </c>
       <c r="F13" t="n">
-        <v>2144.986666666667</v>
+        <v>3866.673733866521</v>
       </c>
       <c r="G13" t="n">
-        <v>2490.68</v>
+        <v>4489.84</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -13206,16 +13206,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>24836</v>
+        <v>29737</v>
       </c>
       <c r="E14" t="n">
-        <v>126.6666666666667</v>
+        <v>152</v>
       </c>
       <c r="F14" t="n">
-        <v>2144.986666666667</v>
+        <v>2568.286266133479</v>
       </c>
       <c r="G14" t="n">
-        <v>2490.68</v>
+        <v>2982.2</v>
       </c>
       <c r="H14" t="n">
         <v>1</v>
@@ -13230,28 +13230,28 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Audio Array-Catch All-Condenser -SB-PT</t>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0B4DPX2J2</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>24836</v>
+        <v>1618</v>
       </c>
       <c r="E15" t="n">
-        <v>126.6666666666667</v>
+        <v>2</v>
       </c>
       <c r="F15" t="n">
-        <v>2144.986666666667</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G15" t="n">
-        <v>2490.68</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -13268,23 +13268,23 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>B0B4DPX2J2</t>
+          <t>B0B4DS678Q</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E16" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G16" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -13301,23 +13301,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B0B4DS678Q</t>
+          <t>B0B4G19R58</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E17" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G17" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -13334,23 +13334,23 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>B0B4G19R58</t>
+          <t>B0B4G1PXWV</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E18" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G18" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -13367,23 +13367,23 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B0B4G1PXWV</t>
+          <t>B0B4G89VQJ</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>21415.38461538462</v>
+        <v>15255</v>
       </c>
       <c r="E19" t="n">
-        <v>78.19230769230769</v>
+        <v>66</v>
       </c>
       <c r="F19" t="n">
-        <v>653.4357692307692</v>
+        <v>523.8426440744703</v>
       </c>
       <c r="G19" t="n">
-        <v>4409.489615384615</v>
+        <v>3935.980542071628</v>
       </c>
       <c r="H19" t="n">
-        <v>1.538461538461539</v>
+        <v>1</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -13400,23 +13400,23 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>B0B4G89VQJ</t>
+          <t>B0B4JRQP22</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E20" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G20" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -13433,23 +13433,23 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>B0B4JRQP22</t>
+          <t>B0B4K87PR4</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21415.38461538462</v>
+        <v>28470</v>
       </c>
       <c r="E21" t="n">
-        <v>78.19230769230769</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
-        <v>653.4357692307692</v>
+        <v>476.7066297565675</v>
       </c>
       <c r="G21" t="n">
-        <v>4409.489615384615</v>
+        <v>7468.79780643741</v>
       </c>
       <c r="H21" t="n">
-        <v>1.538461538461539</v>
+        <v>2</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -13466,23 +13466,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B0B4K87PR4</t>
+          <t>B0B4KC7VBM</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21415.38461538462</v>
+        <v>32646</v>
       </c>
       <c r="E22" t="n">
-        <v>78.19230769230769</v>
+        <v>85</v>
       </c>
       <c r="F22" t="n">
-        <v>653.4357692307692</v>
+        <v>549.7051336010765</v>
       </c>
       <c r="G22" t="n">
-        <v>4409.489615384615</v>
+        <v>8630.512359992565</v>
       </c>
       <c r="H22" t="n">
-        <v>1.538461538461539</v>
+        <v>3</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -13499,23 +13499,23 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B0B4KC7VBM</t>
+          <t>B0BLJVJ2GN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21415.38461538462</v>
+        <v>3623</v>
       </c>
       <c r="E23" t="n">
-        <v>78.19230769230769</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
-        <v>653.4357692307692</v>
+        <v>271.2064483381183</v>
       </c>
       <c r="G23" t="n">
-        <v>4409.489615384615</v>
+        <v>1297.627357987338</v>
       </c>
       <c r="H23" t="n">
-        <v>1.538461538461539</v>
+        <v>1</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -13532,23 +13532,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B0BLJVJ2GN</t>
+          <t>B0BLK8DNPD</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E24" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G24" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -13565,23 +13565,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B0BLK8DNPD</t>
+          <t>B0BPLWW72Y</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>21415.38461538462</v>
+        <v>5368</v>
       </c>
       <c r="E25" t="n">
-        <v>78.19230769230769</v>
+        <v>14</v>
       </c>
       <c r="F25" t="n">
-        <v>653.4357692307692</v>
+        <v>93.82772047655912</v>
       </c>
       <c r="G25" t="n">
-        <v>4409.489615384615</v>
+        <v>1493.195376123082</v>
       </c>
       <c r="H25" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -13602,19 +13602,19 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>21415.38461538462</v>
+        <v>86240</v>
       </c>
       <c r="E26" t="n">
-        <v>78.19230769230769</v>
+        <v>397</v>
       </c>
       <c r="F26" t="n">
-        <v>653.4357692307692</v>
+        <v>3212.195160318498</v>
       </c>
       <c r="G26" t="n">
-        <v>4409.489615384615</v>
+        <v>24424.43979564315</v>
       </c>
       <c r="H26" t="n">
-        <v>1.538461538461539</v>
+        <v>7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -13631,23 +13631,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B0C4YTNJG7</t>
+          <t>B0BPM2T7BQ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>21415.38461538462</v>
+        <v>26455</v>
       </c>
       <c r="E27" t="n">
-        <v>78.19230769230769</v>
+        <v>124</v>
       </c>
       <c r="F27" t="n">
-        <v>653.4357692307692</v>
+        <v>1001.915761918199</v>
       </c>
       <c r="G27" t="n">
-        <v>4409.489615384615</v>
+        <v>7635.79558095005</v>
       </c>
       <c r="H27" t="n">
-        <v>1.538461538461539</v>
+        <v>2</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -13664,23 +13664,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B0CF5R3V95</t>
+          <t>B0C4YTNJG7</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E28" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G28" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -13697,23 +13697,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B0CF5RRTDJ</t>
+          <t>B0CF5R3V95</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21415.38461538462</v>
+        <v>25691</v>
       </c>
       <c r="E29" t="n">
-        <v>78.19230769230769</v>
+        <v>181</v>
       </c>
       <c r="F29" t="n">
-        <v>653.4357692307692</v>
+        <v>1897.155475163351</v>
       </c>
       <c r="G29" t="n">
-        <v>4409.489615384615</v>
+        <v>10690.87966984805</v>
       </c>
       <c r="H29" t="n">
-        <v>1.538461538461539</v>
+        <v>5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -13730,23 +13730,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B0CF5TCQKL</t>
+          <t>B0CF5RRTDJ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>21415.38461538462</v>
+        <v>7236</v>
       </c>
       <c r="E30" t="n">
-        <v>78.19230769230769</v>
+        <v>64</v>
       </c>
       <c r="F30" t="n">
-        <v>653.4357692307692</v>
+        <v>746.7022590345399</v>
       </c>
       <c r="G30" t="n">
-        <v>4409.489615384615</v>
+        <v>3636.443514236245</v>
       </c>
       <c r="H30" t="n">
-        <v>1.538461538461539</v>
+        <v>2</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -13763,23 +13763,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>B0CH4RT4P8</t>
+          <t>B0CF5TCQKL</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>21415.38461538462</v>
+        <v>5977</v>
       </c>
       <c r="E31" t="n">
-        <v>78.19230769230769</v>
+        <v>26</v>
       </c>
       <c r="F31" t="n">
-        <v>653.4357692307692</v>
+        <v>260.3607692307692</v>
       </c>
       <c r="G31" t="n">
-        <v>4409.489615384615</v>
+        <v>3134.75</v>
       </c>
       <c r="H31" t="n">
-        <v>1.538461538461539</v>
+        <v>1</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -13796,23 +13796,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>B0CKHVHVQ1</t>
+          <t>B0CH4RT4P8</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>21415.38461538462</v>
+        <v>12003</v>
       </c>
       <c r="E32" t="n">
-        <v>78.19230769230769</v>
+        <v>50</v>
       </c>
       <c r="F32" t="n">
-        <v>653.4357692307692</v>
+        <v>400.6706287334</v>
       </c>
       <c r="G32" t="n">
-        <v>4409.489615384615</v>
+        <v>2997.262571772998</v>
       </c>
       <c r="H32" t="n">
-        <v>1.538461538461539</v>
+        <v>1</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -13829,23 +13829,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>B0CM6NTWBP</t>
+          <t>B0CKHVHVQ1</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21415.38461538462</v>
+        <v>70094</v>
       </c>
       <c r="E33" t="n">
-        <v>78.19230769230769</v>
+        <v>184</v>
       </c>
       <c r="F33" t="n">
-        <v>653.4357692307692</v>
+        <v>1204.212823858105</v>
       </c>
       <c r="G33" t="n">
-        <v>4409.489615384615</v>
+        <v>19046.49445744694</v>
       </c>
       <c r="H33" t="n">
-        <v>1.538461538461539</v>
+        <v>6</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -13862,23 +13862,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>B0D3M1B4Z8</t>
+          <t>B0CM6NTWBP</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>21415.38461538462</v>
+        <v>12107</v>
       </c>
       <c r="E34" t="n">
-        <v>78.19230769230769</v>
+        <v>51</v>
       </c>
       <c r="F34" t="n">
-        <v>653.4357692307692</v>
+        <v>404.6312643133032</v>
       </c>
       <c r="G34" t="n">
-        <v>4409.489615384615</v>
+        <v>3027.447348585849</v>
       </c>
       <c r="H34" t="n">
-        <v>1.538461538461539</v>
+        <v>1</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -13895,23 +13895,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>B0DFMNGFTD</t>
+          <t>B0D3M1B4Z8</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>21415.38461538462</v>
+        <v>111581</v>
       </c>
       <c r="E35" t="n">
-        <v>78.19230769230769</v>
+        <v>410</v>
       </c>
       <c r="F35" t="n">
-        <v>653.4357692307692</v>
+        <v>3943.090769230769</v>
       </c>
       <c r="G35" t="n">
-        <v>4409.489615384615</v>
+        <v>5964.4</v>
       </c>
       <c r="H35" t="n">
-        <v>1.538461538461539</v>
+        <v>2</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -13928,23 +13928,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>B0DT6T6N6B</t>
+          <t>B0DFMNGFTD</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E36" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F36" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G36" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -13961,23 +13961,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>B0FF9R3GKK</t>
+          <t>B0DN6PFWNK</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>21415.38461538462</v>
+        <v>18184</v>
       </c>
       <c r="E37" t="n">
-        <v>78.19230769230769</v>
+        <v>85</v>
       </c>
       <c r="F37" t="n">
-        <v>653.4357692307692</v>
+        <v>688.6457427215058</v>
       </c>
       <c r="G37" t="n">
-        <v>4409.489615384615</v>
+        <v>5248.303618904695</v>
       </c>
       <c r="H37" t="n">
-        <v>1.538461538461539</v>
+        <v>2</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -13994,23 +13994,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>B0G2C2RCXN</t>
+          <t>B0DT6T6N6B</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E38" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F38" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G38" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -14027,23 +14027,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>B0G3Q517Y2</t>
+          <t>B0FF9R3GKK</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E39" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G39" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -14060,23 +14060,23 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>B0G3Q59X8C</t>
+          <t>B0G2C2RCXN</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E40" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F40" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G40" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -14093,23 +14093,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>B0G4DNF8RZ</t>
+          <t>B0G3Q517Y2</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>21415.38461538462</v>
+        <v>1618</v>
       </c>
       <c r="E41" t="n">
-        <v>78.19230769230769</v>
+        <v>2</v>
       </c>
       <c r="F41" t="n">
-        <v>653.4357692307692</v>
+        <v>7.39076923076923</v>
       </c>
       <c r="G41" t="n">
-        <v>4409.489615384615</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.538461538461539</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -14121,30 +14121,96 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>B0G3Q59X8C</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>28365</v>
+      </c>
+      <c r="E42" t="n">
+        <v>65</v>
+      </c>
+      <c r="F42" t="n">
+        <v>449.8050788006295</v>
+      </c>
+      <c r="G42" t="n">
+        <v>2197.257304748154</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Audio Array-Multiple Ad Group-SB-PT</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>B0G4DNF8RZ</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>48084</v>
+      </c>
+      <c r="E43" t="n">
+        <v>112</v>
+      </c>
+      <c r="F43" t="n">
+        <v>775.9664596609089</v>
+      </c>
+      <c r="G43" t="n">
+        <v>3817.142695251845</v>
+      </c>
+      <c r="H43" t="n">
+        <v>2</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Audio Array</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>Ton_Condenser_TC-777_SBV_KT</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>B07WLWN2ZT</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D44" t="n">
         <v>486</v>
       </c>
-      <c r="E42" t="n">
+      <c r="E44" t="n">
         <v>2</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F44" t="n">
         <v>88.87</v>
       </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" t="inlineStr">
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
         <is>
           <t>Audio Array</t>
         </is>

--- a/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
+++ b/data/ams_weekly_data/Audio_Array/ads_report_week14.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="SP" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="SD" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="SB" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SP" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SD" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SB" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
